--- a/Excel/AAA/C0382C01tracking_codes.xlsx
+++ b/Excel/AAA/C0382C01tracking_codes.xlsx
@@ -14,606 +14,1506 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="500">
+  <si>
+    <t>TAHER21-C0382C01-AAA1398</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1332</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1780</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1685</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1610</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1776</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1575</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1305</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1906</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1081</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1959</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1785</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1925</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1614</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1706</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1386</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1544</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1462</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1092</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1716</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1192</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1493</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1173</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1447</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1784</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1971</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1739</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1845</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1815</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1389</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1604</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1323</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1516</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1832</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1840</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1660</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1251</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1249</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1268</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1578</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1940</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1087</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1127</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1291</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1261</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1880</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1136</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1222</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1503</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1405</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1682</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1244</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1379</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1812</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1282</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1713</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1547</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1245</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1318</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1019</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1520</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1781</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1293</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1193</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1167</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1659</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1133</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1143</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1038</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1402</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1691</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1470</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1853</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1198</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1077</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1975</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1112</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1068</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1597</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1350</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1800</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1506</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1130</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1847</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1626</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1961</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1508</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1227</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1171</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1751</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1280</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1715</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1846</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1266</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1309</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1240</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1932</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1798</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1827</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1502</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1619</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1411</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1532</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1501</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1420</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1499</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1110</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1093</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1600</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1729</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1669</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1450</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1663</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1066</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1454</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1326</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1365</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1641</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1425</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1042</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1421</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1264</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1012</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1742</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1242</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1521</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1960</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1896</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1181</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1106</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1408</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1089</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1430</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1888</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1539</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1230</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1558</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1955</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1203</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1484</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1163</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1725</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1883</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1243</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1586</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1692</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1048</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1254</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1771</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1866</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1327</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1553</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1302</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1605</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1451</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1149</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1267</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1434</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1461</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1362</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1885</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1562</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1879</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1082</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1107</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1121</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1819</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1446</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1946</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1333</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1401</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1569</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1246</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1629</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1858</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1166</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1312</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1969</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1928</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1239</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1869</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1571</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1128</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1809</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1397</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1789</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1449</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1005</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1021</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1117</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1611</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1750</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1655</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1721</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1881</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1701</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1448</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1055</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1417</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1717</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1588</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1480</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1714</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1140</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1882</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1938</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1536</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1342</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1464</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1288</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1108</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1294</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1820</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1774</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1415</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1518</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1664</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1648</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1540</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1987</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1119</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1565</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1855</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1440</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1311</t>
+  </si>
   <si>
     <t>TAHER21-C0382C01-AAA1436</t>
   </si>
   <si>
-    <t>TAHER21-C0382C01-AAA1383</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1421</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1128</t>
+    <t>TAHER21-C0382C01-AAA1662</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1892</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1147</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1720</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1085</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1361</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1719</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1621</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1796</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1406</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1852</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1674</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1102</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1923</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1416</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1807</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1040</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1075</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1035</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1366</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1645</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1901</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1683</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1252</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1131</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1559</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1875</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1341</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1208</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1913</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1902</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1469</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1762</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1758</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1233</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1816</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1476</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1328</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1031</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1283</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1277</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1803</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1041</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1058</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1174</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1074</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1067</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1235</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1900</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1899</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1497</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1772</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1564</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1665</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1929</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1116</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1915</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1070</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1554</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1330</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1795</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1441</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1754</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1029</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1821</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1944</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1657</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1679</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1334</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1098</t>
   </si>
   <si>
     <t>TAHER21-C0382C01-AAA1132</t>
   </si>
   <si>
-    <t>TAHER21-C0382C01-AAA1179</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1389</t>
+    <t>TAHER21-C0382C01-AAA1349</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1907</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1238</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1615</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1073</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1351</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1681</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1161</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1775</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1942</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1947</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1037</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1695</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1278</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1260</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1904</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1631</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1157</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1078</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1935</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1723</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1024</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1921</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1007</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1498</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1560</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1458</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1957</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1693</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1783</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1537</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1546</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1738</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1509</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1699</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1919</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1830</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1380</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1856</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1443</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1587</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1322</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1347</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1778</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1460</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1857</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1006</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1025</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1296</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1570</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1550</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1638</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1170</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1124</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1962</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1135</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1624</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1015</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1211</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1646</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1109</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1414</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1728</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1169</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1096</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1183</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1453</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1654</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1522</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1428</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1276</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1191</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1523</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1022</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1740</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1046</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1358</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1787</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1500</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1368</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1263</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1737</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1950</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1711</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1165</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1013</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1698</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1918</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1424</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1805</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1861</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1387</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1910</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1494</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1628</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1612</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1091</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1003</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1761</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1001</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1490</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1262</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1099</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1100</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1210</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1274</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1195</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1905</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1286</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1618</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1700</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1768</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1213</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1835</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1863</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1369</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1703</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1009</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1496</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1953</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1998</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1593</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1050</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1032</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1596</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1465</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1534</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1724</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1033</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1734</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1036</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1702</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1177</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1556</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1485</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1974</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1831</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1212</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1372</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1786</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1164</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1903</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1385</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1020</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1854</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1838</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1639</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1984</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1250</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1241</t>
   </si>
   <si>
     <t>TAHER21-C0382C01-AAA1352</t>
   </si>
   <si>
-    <t>TAHER21-C0382C01-AAA1407</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1288</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1152</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1413</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1117</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1451</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1093</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1329</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1363</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1424</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1274</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1001</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1272</t>
+    <t>TAHER21-C0382C01-AAA1289</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1063</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1640</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1951</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1573</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1168</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1868</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1432</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1908</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1049</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1120</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1788</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1444</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1579</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1355</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1468</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1201</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1504</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1891</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1527</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1507</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1843</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1766</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1090</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1373</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1150</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1335</t>
   </si>
   <si>
     <t>TAHER21-C0382C01-AAA1088</t>
   </si>
   <si>
-    <t>TAHER21-C0382C01-AAA1212</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1240</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1379</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1139</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1143</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1069</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1169</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1354</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1130</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1158</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1106</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1268</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1201</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1455</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1425</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1115</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1420</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1151</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1123</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1131</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1322</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1323</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1021</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1203</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1227</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1178</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1011</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1049</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1056</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1299</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1374</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1232</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1191</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1161</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1412</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1254</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1417</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1485</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1196</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1084</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1067</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1403</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1309</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1369</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1303</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1229</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1174</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1478</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1266</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1411</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1176</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1214</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1027</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1167</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1124</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1252</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1496</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1035</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1008</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1255</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1330</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1228</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1481</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1321</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1020</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1037</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1476</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1206</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1095</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1486</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1263</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1328</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1090</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1304</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1262</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1430</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1250</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1043</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1126</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1080</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1390</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1339</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1334</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1064</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1282</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1189</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1357</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1326</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1351</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1079</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1075</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1414</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1241</t>
+    <t>TAHER21-C0382C01-AAA1400</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1810</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1308</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1967</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1948</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1872</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1377</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1732</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1964</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1028</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1837</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1584</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1627</t>
   </si>
   <si>
     <t>TAHER21-C0382C01-AAA1409</t>
   </si>
   <si>
-    <t>TAHER21-C0382C01-AAA1112</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1006</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1215</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1159</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1465</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1070</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1172</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1366</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1435</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1257</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1135</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1046</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1050</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1318</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1078</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1104</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1057</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1482</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1346</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1218</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1247</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1089</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1498</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1387</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1025</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1073</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1197</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1468</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1490</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1284</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1009</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1418</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1058</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1225</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1251</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1224</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1396</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1371</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1216</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1217</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1100</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1248</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1140</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1302</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1036</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1373</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1365</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1199</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1445</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1108</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1156</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1003</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1204</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1208</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1177</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1470</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1071</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1022</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1286</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1105</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1283</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1305</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1361</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1031</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1111</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1289</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1356</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1053</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1051</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1065</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1122</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1388</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1164</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1076</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1119</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1154</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1399</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1060</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1188</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1395</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1209</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1273</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1401</t>
-  </si>
-  <si>
-    <t>TAHER21-C0382C01-AAA1175</t>
+    <t>TAHER21-C0382C01-AAA1566</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1886</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1763</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1495</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1094</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1823</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1609</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1749</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1129</t>
+  </si>
+  <si>
+    <t>TAHER21-C0382C01-AAA1924</t>
   </si>
 </sst>
 </file>
@@ -971,7 +1871,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B201"/>
+  <dimension ref="A1:B501"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2579,6 +3479,2406 @@
         <v>199</v>
       </c>
     </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="1">
+        <v>200</v>
+      </c>
+      <c r="B202" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="1">
+        <v>201</v>
+      </c>
+      <c r="B203" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" s="1">
+        <v>202</v>
+      </c>
+      <c r="B204" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="1">
+        <v>203</v>
+      </c>
+      <c r="B205" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="1">
+        <v>204</v>
+      </c>
+      <c r="B206" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="1">
+        <v>205</v>
+      </c>
+      <c r="B207" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="1">
+        <v>206</v>
+      </c>
+      <c r="B208" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="1">
+        <v>207</v>
+      </c>
+      <c r="B209" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" s="1">
+        <v>208</v>
+      </c>
+      <c r="B210" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" s="1">
+        <v>209</v>
+      </c>
+      <c r="B211" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="1">
+        <v>210</v>
+      </c>
+      <c r="B212" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="1">
+        <v>211</v>
+      </c>
+      <c r="B213" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="1">
+        <v>212</v>
+      </c>
+      <c r="B214" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="1">
+        <v>213</v>
+      </c>
+      <c r="B215" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" s="1">
+        <v>214</v>
+      </c>
+      <c r="B216" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="1">
+        <v>215</v>
+      </c>
+      <c r="B217" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="1">
+        <v>216</v>
+      </c>
+      <c r="B218" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="1">
+        <v>217</v>
+      </c>
+      <c r="B219" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" s="1">
+        <v>218</v>
+      </c>
+      <c r="B220" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" s="1">
+        <v>219</v>
+      </c>
+      <c r="B221" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="1">
+        <v>220</v>
+      </c>
+      <c r="B222" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" s="1">
+        <v>221</v>
+      </c>
+      <c r="B223" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="1">
+        <v>222</v>
+      </c>
+      <c r="B224" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="1">
+        <v>223</v>
+      </c>
+      <c r="B225" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" s="1">
+        <v>224</v>
+      </c>
+      <c r="B226" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" s="1">
+        <v>225</v>
+      </c>
+      <c r="B227" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" s="1">
+        <v>226</v>
+      </c>
+      <c r="B228" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" s="1">
+        <v>227</v>
+      </c>
+      <c r="B229" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" s="1">
+        <v>228</v>
+      </c>
+      <c r="B230" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" s="1">
+        <v>229</v>
+      </c>
+      <c r="B231" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" s="1">
+        <v>230</v>
+      </c>
+      <c r="B232" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" s="1">
+        <v>231</v>
+      </c>
+      <c r="B233" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" s="1">
+        <v>232</v>
+      </c>
+      <c r="B234" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" s="1">
+        <v>233</v>
+      </c>
+      <c r="B235" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" s="1">
+        <v>234</v>
+      </c>
+      <c r="B236" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" s="1">
+        <v>235</v>
+      </c>
+      <c r="B237" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" s="1">
+        <v>236</v>
+      </c>
+      <c r="B238" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" s="1">
+        <v>237</v>
+      </c>
+      <c r="B239" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" s="1">
+        <v>238</v>
+      </c>
+      <c r="B240" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" s="1">
+        <v>239</v>
+      </c>
+      <c r="B241" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" s="1">
+        <v>240</v>
+      </c>
+      <c r="B242" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" s="1">
+        <v>241</v>
+      </c>
+      <c r="B243" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244" s="1">
+        <v>242</v>
+      </c>
+      <c r="B244" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245" s="1">
+        <v>243</v>
+      </c>
+      <c r="B245" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246" s="1">
+        <v>244</v>
+      </c>
+      <c r="B246" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247" s="1">
+        <v>245</v>
+      </c>
+      <c r="B247" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" s="1">
+        <v>246</v>
+      </c>
+      <c r="B248" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249" s="1">
+        <v>247</v>
+      </c>
+      <c r="B249" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" s="1">
+        <v>248</v>
+      </c>
+      <c r="B250" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251" s="1">
+        <v>249</v>
+      </c>
+      <c r="B251" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" s="1">
+        <v>250</v>
+      </c>
+      <c r="B252" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" s="1">
+        <v>251</v>
+      </c>
+      <c r="B253" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" s="1">
+        <v>252</v>
+      </c>
+      <c r="B254" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" s="1">
+        <v>253</v>
+      </c>
+      <c r="B255" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" s="1">
+        <v>254</v>
+      </c>
+      <c r="B256" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" s="1">
+        <v>255</v>
+      </c>
+      <c r="B257" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" s="1">
+        <v>256</v>
+      </c>
+      <c r="B258" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" s="1">
+        <v>257</v>
+      </c>
+      <c r="B259" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="1">
+        <v>258</v>
+      </c>
+      <c r="B260" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261" s="1">
+        <v>259</v>
+      </c>
+      <c r="B261" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" s="1">
+        <v>260</v>
+      </c>
+      <c r="B262" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" s="1">
+        <v>261</v>
+      </c>
+      <c r="B263" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264" s="1">
+        <v>262</v>
+      </c>
+      <c r="B264" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265" s="1">
+        <v>263</v>
+      </c>
+      <c r="B265" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266" s="1">
+        <v>264</v>
+      </c>
+      <c r="B266" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267" s="1">
+        <v>265</v>
+      </c>
+      <c r="B267" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" s="1">
+        <v>266</v>
+      </c>
+      <c r="B268" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" s="1">
+        <v>267</v>
+      </c>
+      <c r="B269" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270" s="1">
+        <v>268</v>
+      </c>
+      <c r="B270" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271" s="1">
+        <v>269</v>
+      </c>
+      <c r="B271" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272" s="1">
+        <v>270</v>
+      </c>
+      <c r="B272" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" s="1">
+        <v>271</v>
+      </c>
+      <c r="B273" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" s="1">
+        <v>272</v>
+      </c>
+      <c r="B274" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" s="1">
+        <v>273</v>
+      </c>
+      <c r="B275" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276" s="1">
+        <v>274</v>
+      </c>
+      <c r="B276" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277" s="1">
+        <v>275</v>
+      </c>
+      <c r="B277" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278" s="1">
+        <v>276</v>
+      </c>
+      <c r="B278" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279" s="1">
+        <v>277</v>
+      </c>
+      <c r="B279" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280" s="1">
+        <v>278</v>
+      </c>
+      <c r="B280" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281" s="1">
+        <v>279</v>
+      </c>
+      <c r="B281" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282" s="1">
+        <v>280</v>
+      </c>
+      <c r="B282" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283" s="1">
+        <v>281</v>
+      </c>
+      <c r="B283" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284" s="1">
+        <v>282</v>
+      </c>
+      <c r="B284" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285" s="1">
+        <v>283</v>
+      </c>
+      <c r="B285" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286" s="1">
+        <v>284</v>
+      </c>
+      <c r="B286" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287" s="1">
+        <v>285</v>
+      </c>
+      <c r="B287" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288" s="1">
+        <v>286</v>
+      </c>
+      <c r="B288" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" s="1">
+        <v>287</v>
+      </c>
+      <c r="B289" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290" s="1">
+        <v>288</v>
+      </c>
+      <c r="B290" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291" s="1">
+        <v>289</v>
+      </c>
+      <c r="B291" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" s="1">
+        <v>290</v>
+      </c>
+      <c r="B292" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293" s="1">
+        <v>291</v>
+      </c>
+      <c r="B293" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294" s="1">
+        <v>292</v>
+      </c>
+      <c r="B294" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" s="1">
+        <v>293</v>
+      </c>
+      <c r="B295" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296" s="1">
+        <v>294</v>
+      </c>
+      <c r="B296" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" s="1">
+        <v>295</v>
+      </c>
+      <c r="B297" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298" s="1">
+        <v>296</v>
+      </c>
+      <c r="B298" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" s="1">
+        <v>297</v>
+      </c>
+      <c r="B299" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300" s="1">
+        <v>298</v>
+      </c>
+      <c r="B300" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301" s="1">
+        <v>299</v>
+      </c>
+      <c r="B301" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302" s="1">
+        <v>300</v>
+      </c>
+      <c r="B302" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303" s="1">
+        <v>301</v>
+      </c>
+      <c r="B303" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304" s="1">
+        <v>302</v>
+      </c>
+      <c r="B304" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305" s="1">
+        <v>303</v>
+      </c>
+      <c r="B305" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306" s="1">
+        <v>304</v>
+      </c>
+      <c r="B306" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307" s="1">
+        <v>305</v>
+      </c>
+      <c r="B307" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" s="1">
+        <v>306</v>
+      </c>
+      <c r="B308" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309" s="1">
+        <v>307</v>
+      </c>
+      <c r="B309" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310" s="1">
+        <v>308</v>
+      </c>
+      <c r="B310" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311" s="1">
+        <v>309</v>
+      </c>
+      <c r="B311" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312" s="1">
+        <v>310</v>
+      </c>
+      <c r="B312" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313" s="1">
+        <v>311</v>
+      </c>
+      <c r="B313" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" s="1">
+        <v>312</v>
+      </c>
+      <c r="B314" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315" s="1">
+        <v>313</v>
+      </c>
+      <c r="B315" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316" s="1">
+        <v>314</v>
+      </c>
+      <c r="B316" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317" s="1">
+        <v>315</v>
+      </c>
+      <c r="B317" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318" s="1">
+        <v>316</v>
+      </c>
+      <c r="B318" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319" s="1">
+        <v>317</v>
+      </c>
+      <c r="B319" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320" s="1">
+        <v>318</v>
+      </c>
+      <c r="B320" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321" s="1">
+        <v>319</v>
+      </c>
+      <c r="B321" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322" s="1">
+        <v>320</v>
+      </c>
+      <c r="B322" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323" s="1">
+        <v>321</v>
+      </c>
+      <c r="B323" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324" s="1">
+        <v>322</v>
+      </c>
+      <c r="B324" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325" s="1">
+        <v>323</v>
+      </c>
+      <c r="B325" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326" s="1">
+        <v>324</v>
+      </c>
+      <c r="B326" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327" s="1">
+        <v>325</v>
+      </c>
+      <c r="B327" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328" s="1">
+        <v>326</v>
+      </c>
+      <c r="B328" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329" s="1">
+        <v>327</v>
+      </c>
+      <c r="B329" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330" s="1">
+        <v>328</v>
+      </c>
+      <c r="B330" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331" s="1">
+        <v>329</v>
+      </c>
+      <c r="B331" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332" s="1">
+        <v>330</v>
+      </c>
+      <c r="B332" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333" s="1">
+        <v>331</v>
+      </c>
+      <c r="B333" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334" s="1">
+        <v>332</v>
+      </c>
+      <c r="B334" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335" s="1">
+        <v>333</v>
+      </c>
+      <c r="B335" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336" s="1">
+        <v>334</v>
+      </c>
+      <c r="B336" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337" s="1">
+        <v>335</v>
+      </c>
+      <c r="B337" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338" s="1">
+        <v>336</v>
+      </c>
+      <c r="B338" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" s="1">
+        <v>337</v>
+      </c>
+      <c r="B339" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340" s="1">
+        <v>338</v>
+      </c>
+      <c r="B340" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341" s="1">
+        <v>339</v>
+      </c>
+      <c r="B341" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342" s="1">
+        <v>340</v>
+      </c>
+      <c r="B342" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343" s="1">
+        <v>341</v>
+      </c>
+      <c r="B343" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344" s="1">
+        <v>342</v>
+      </c>
+      <c r="B344" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345" s="1">
+        <v>343</v>
+      </c>
+      <c r="B345" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" s="1">
+        <v>344</v>
+      </c>
+      <c r="B346" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347" s="1">
+        <v>345</v>
+      </c>
+      <c r="B347" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348" s="1">
+        <v>346</v>
+      </c>
+      <c r="B348" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349" s="1">
+        <v>347</v>
+      </c>
+      <c r="B349" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350" s="1">
+        <v>348</v>
+      </c>
+      <c r="B350" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351" s="1">
+        <v>349</v>
+      </c>
+      <c r="B351" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352" s="1">
+        <v>350</v>
+      </c>
+      <c r="B352" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353" s="1">
+        <v>351</v>
+      </c>
+      <c r="B353" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354" s="1">
+        <v>352</v>
+      </c>
+      <c r="B354" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355" s="1">
+        <v>353</v>
+      </c>
+      <c r="B355" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356" s="1">
+        <v>354</v>
+      </c>
+      <c r="B356" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357" s="1">
+        <v>355</v>
+      </c>
+      <c r="B357" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358" s="1">
+        <v>356</v>
+      </c>
+      <c r="B358" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359" s="1">
+        <v>357</v>
+      </c>
+      <c r="B359" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360" s="1">
+        <v>358</v>
+      </c>
+      <c r="B360" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" s="1">
+        <v>359</v>
+      </c>
+      <c r="B361" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" s="1">
+        <v>360</v>
+      </c>
+      <c r="B362" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" s="1">
+        <v>361</v>
+      </c>
+      <c r="B363" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" s="1">
+        <v>362</v>
+      </c>
+      <c r="B364" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" s="1">
+        <v>363</v>
+      </c>
+      <c r="B365" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" s="1">
+        <v>364</v>
+      </c>
+      <c r="B366" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" s="1">
+        <v>365</v>
+      </c>
+      <c r="B367" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" s="1">
+        <v>366</v>
+      </c>
+      <c r="B368" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" s="1">
+        <v>367</v>
+      </c>
+      <c r="B369" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" s="1">
+        <v>368</v>
+      </c>
+      <c r="B370" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" s="1">
+        <v>369</v>
+      </c>
+      <c r="B371" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" s="1">
+        <v>370</v>
+      </c>
+      <c r="B372" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373" s="1">
+        <v>371</v>
+      </c>
+      <c r="B373" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374" s="1">
+        <v>372</v>
+      </c>
+      <c r="B374" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375" s="1">
+        <v>373</v>
+      </c>
+      <c r="B375" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376" s="1">
+        <v>374</v>
+      </c>
+      <c r="B376" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377" s="1">
+        <v>375</v>
+      </c>
+      <c r="B377" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378" s="1">
+        <v>376</v>
+      </c>
+      <c r="B378" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379" s="1">
+        <v>377</v>
+      </c>
+      <c r="B379" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" s="1">
+        <v>378</v>
+      </c>
+      <c r="B380" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381" s="1">
+        <v>379</v>
+      </c>
+      <c r="B381" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382" s="1">
+        <v>380</v>
+      </c>
+      <c r="B382" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383" s="1">
+        <v>381</v>
+      </c>
+      <c r="B383" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384" s="1">
+        <v>382</v>
+      </c>
+      <c r="B384" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385" s="1">
+        <v>383</v>
+      </c>
+      <c r="B385" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386" s="1">
+        <v>384</v>
+      </c>
+      <c r="B386" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387" s="1">
+        <v>385</v>
+      </c>
+      <c r="B387" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388" s="1">
+        <v>386</v>
+      </c>
+      <c r="B388" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389" s="1">
+        <v>387</v>
+      </c>
+      <c r="B389" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390" s="1">
+        <v>388</v>
+      </c>
+      <c r="B390" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391" s="1">
+        <v>389</v>
+      </c>
+      <c r="B391" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392" s="1">
+        <v>390</v>
+      </c>
+      <c r="B392" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393" s="1">
+        <v>391</v>
+      </c>
+      <c r="B393" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394" s="1">
+        <v>392</v>
+      </c>
+      <c r="B394" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395" s="1">
+        <v>393</v>
+      </c>
+      <c r="B395" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396" s="1">
+        <v>394</v>
+      </c>
+      <c r="B396" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397" s="1">
+        <v>395</v>
+      </c>
+      <c r="B397" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398" s="1">
+        <v>396</v>
+      </c>
+      <c r="B398" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399" s="1">
+        <v>397</v>
+      </c>
+      <c r="B399" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400" s="1">
+        <v>398</v>
+      </c>
+      <c r="B400" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401" s="1">
+        <v>399</v>
+      </c>
+      <c r="B401" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402" s="1">
+        <v>400</v>
+      </c>
+      <c r="B402" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403" s="1">
+        <v>401</v>
+      </c>
+      <c r="B403" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404" s="1">
+        <v>402</v>
+      </c>
+      <c r="B404" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405" s="1">
+        <v>403</v>
+      </c>
+      <c r="B405" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406" s="1">
+        <v>404</v>
+      </c>
+      <c r="B406" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407" s="1">
+        <v>405</v>
+      </c>
+      <c r="B407" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408" s="1">
+        <v>406</v>
+      </c>
+      <c r="B408" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409" s="1">
+        <v>407</v>
+      </c>
+      <c r="B409" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410" s="1">
+        <v>408</v>
+      </c>
+      <c r="B410" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411" s="1">
+        <v>409</v>
+      </c>
+      <c r="B411" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412" s="1">
+        <v>410</v>
+      </c>
+      <c r="B412" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413" s="1">
+        <v>411</v>
+      </c>
+      <c r="B413" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414" s="1">
+        <v>412</v>
+      </c>
+      <c r="B414" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415" s="1">
+        <v>413</v>
+      </c>
+      <c r="B415" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416" s="1">
+        <v>414</v>
+      </c>
+      <c r="B416" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417" s="1">
+        <v>415</v>
+      </c>
+      <c r="B417" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418" s="1">
+        <v>416</v>
+      </c>
+      <c r="B418" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419" s="1">
+        <v>417</v>
+      </c>
+      <c r="B419" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420" s="1">
+        <v>418</v>
+      </c>
+      <c r="B420" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421" s="1">
+        <v>419</v>
+      </c>
+      <c r="B421" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422" s="1">
+        <v>420</v>
+      </c>
+      <c r="B422" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423" s="1">
+        <v>421</v>
+      </c>
+      <c r="B423" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424" s="1">
+        <v>422</v>
+      </c>
+      <c r="B424" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425" s="1">
+        <v>423</v>
+      </c>
+      <c r="B425" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426" s="1">
+        <v>424</v>
+      </c>
+      <c r="B426" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427" s="1">
+        <v>425</v>
+      </c>
+      <c r="B427" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428" s="1">
+        <v>426</v>
+      </c>
+      <c r="B428" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429" s="1">
+        <v>427</v>
+      </c>
+      <c r="B429" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430" s="1">
+        <v>428</v>
+      </c>
+      <c r="B430" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431" s="1">
+        <v>429</v>
+      </c>
+      <c r="B431" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432" s="1">
+        <v>430</v>
+      </c>
+      <c r="B432" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433" s="1">
+        <v>431</v>
+      </c>
+      <c r="B433" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434" s="1">
+        <v>432</v>
+      </c>
+      <c r="B434" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435" s="1">
+        <v>433</v>
+      </c>
+      <c r="B435" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436" s="1">
+        <v>434</v>
+      </c>
+      <c r="B436" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437" s="1">
+        <v>435</v>
+      </c>
+      <c r="B437" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438" s="1">
+        <v>436</v>
+      </c>
+      <c r="B438" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439" s="1">
+        <v>437</v>
+      </c>
+      <c r="B439" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440" s="1">
+        <v>438</v>
+      </c>
+      <c r="B440" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441" s="1">
+        <v>439</v>
+      </c>
+      <c r="B441" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442" s="1">
+        <v>440</v>
+      </c>
+      <c r="B442" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443" s="1">
+        <v>441</v>
+      </c>
+      <c r="B443" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444" s="1">
+        <v>442</v>
+      </c>
+      <c r="B444" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445" s="1">
+        <v>443</v>
+      </c>
+      <c r="B445" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446" s="1">
+        <v>444</v>
+      </c>
+      <c r="B446" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447" s="1">
+        <v>445</v>
+      </c>
+      <c r="B447" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448" s="1">
+        <v>446</v>
+      </c>
+      <c r="B448" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449" s="1">
+        <v>447</v>
+      </c>
+      <c r="B449" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450" s="1">
+        <v>448</v>
+      </c>
+      <c r="B450" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451" s="1">
+        <v>449</v>
+      </c>
+      <c r="B451" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452" s="1">
+        <v>450</v>
+      </c>
+      <c r="B452" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453" s="1">
+        <v>451</v>
+      </c>
+      <c r="B453" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454" s="1">
+        <v>452</v>
+      </c>
+      <c r="B454" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455" s="1">
+        <v>453</v>
+      </c>
+      <c r="B455" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456" s="1">
+        <v>454</v>
+      </c>
+      <c r="B456" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457" s="1">
+        <v>455</v>
+      </c>
+      <c r="B457" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458" s="1">
+        <v>456</v>
+      </c>
+      <c r="B458" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459" s="1">
+        <v>457</v>
+      </c>
+      <c r="B459" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460" s="1">
+        <v>458</v>
+      </c>
+      <c r="B460" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461" s="1">
+        <v>459</v>
+      </c>
+      <c r="B461" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462" s="1">
+        <v>460</v>
+      </c>
+      <c r="B462" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463" s="1">
+        <v>461</v>
+      </c>
+      <c r="B463" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464" s="1">
+        <v>462</v>
+      </c>
+      <c r="B464" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465" s="1">
+        <v>463</v>
+      </c>
+      <c r="B465" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466" s="1">
+        <v>464</v>
+      </c>
+      <c r="B466" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467" s="1">
+        <v>465</v>
+      </c>
+      <c r="B467" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468" s="1">
+        <v>466</v>
+      </c>
+      <c r="B468" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469" s="1">
+        <v>467</v>
+      </c>
+      <c r="B469" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470" s="1">
+        <v>468</v>
+      </c>
+      <c r="B470" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471" s="1">
+        <v>469</v>
+      </c>
+      <c r="B471" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472" s="1">
+        <v>470</v>
+      </c>
+      <c r="B472" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473" s="1">
+        <v>471</v>
+      </c>
+      <c r="B473" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474" s="1">
+        <v>472</v>
+      </c>
+      <c r="B474" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475" s="1">
+        <v>473</v>
+      </c>
+      <c r="B475" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476" s="1">
+        <v>474</v>
+      </c>
+      <c r="B476" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477" s="1">
+        <v>475</v>
+      </c>
+      <c r="B477" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478" s="1">
+        <v>476</v>
+      </c>
+      <c r="B478" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479" s="1">
+        <v>477</v>
+      </c>
+      <c r="B479" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480" s="1">
+        <v>478</v>
+      </c>
+      <c r="B480" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481" s="1">
+        <v>479</v>
+      </c>
+      <c r="B481" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482" s="1">
+        <v>480</v>
+      </c>
+      <c r="B482" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2">
+      <c r="A483" s="1">
+        <v>481</v>
+      </c>
+      <c r="B483" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2">
+      <c r="A484" s="1">
+        <v>482</v>
+      </c>
+      <c r="B484" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2">
+      <c r="A485" s="1">
+        <v>483</v>
+      </c>
+      <c r="B485" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486" s="1">
+        <v>484</v>
+      </c>
+      <c r="B486" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2">
+      <c r="A487" s="1">
+        <v>485</v>
+      </c>
+      <c r="B487" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2">
+      <c r="A488" s="1">
+        <v>486</v>
+      </c>
+      <c r="B488" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2">
+      <c r="A489" s="1">
+        <v>487</v>
+      </c>
+      <c r="B489" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2">
+      <c r="A490" s="1">
+        <v>488</v>
+      </c>
+      <c r="B490" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2">
+      <c r="A491" s="1">
+        <v>489</v>
+      </c>
+      <c r="B491" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2">
+      <c r="A492" s="1">
+        <v>490</v>
+      </c>
+      <c r="B492" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2">
+      <c r="A493" s="1">
+        <v>491</v>
+      </c>
+      <c r="B493" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2">
+      <c r="A494" s="1">
+        <v>492</v>
+      </c>
+      <c r="B494" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2">
+      <c r="A495" s="1">
+        <v>493</v>
+      </c>
+      <c r="B495" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2">
+      <c r="A496" s="1">
+        <v>494</v>
+      </c>
+      <c r="B496" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2">
+      <c r="A497" s="1">
+        <v>495</v>
+      </c>
+      <c r="B497" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2">
+      <c r="A498" s="1">
+        <v>496</v>
+      </c>
+      <c r="B498" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2">
+      <c r="A499" s="1">
+        <v>497</v>
+      </c>
+      <c r="B499" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2">
+      <c r="A500" s="1">
+        <v>498</v>
+      </c>
+      <c r="B500" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2">
+      <c r="A501" s="1">
+        <v>499</v>
+      </c>
+      <c r="B501" t="s">
+        <v>499</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
